--- a/review/etnografiya/may-december/october/october.xlsx
+++ b/review/etnografiya/may-december/october/october.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему одного визита могло быть недостаточно?</t>
+          <t xml:space="preserve">Сватовство не обязательно заканчивается первым визитом. Свадебная договорённость складывается по местному порядку, соединяя несколько действий и встреч.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что могли узнавать о будущей семье до свадьбы?</t>
+          <t xml:space="preserve">Перед браком знакомятся с другим хозяйством. Смотр дома показывает, что новая семейная связь касается повседневного устройства жизни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как люди обозначали, что договорённость состоялась?</t>
+          <t xml:space="preserve">Рукобитье делает договорённость видимой. Жест становится частью местного свадебного порядка, по которому окружающие узнают о принятом решении.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у большого обряда так много помощников?</t>
+          <t xml:space="preserve">Дружка, сваха и подруги выполняют разные свадебные роли. Общий праздник держится на людях, которым поручены конкретные действия.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сообщить о событии без общего чата?</t>
+          <t xml:space="preserve">Приглашение разносит свадебную новость по селу. Будущая встреча начинается раньше застолья — с личного обращения и принятого способа звать гостей.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в общении подруг перед свадьбой?</t>
+          <t xml:space="preserve">Девичник собирает прежний круг перед переменой. Праздничная встреча сохраняет момент, когда отношения подруг получают новое продолжение.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему волосы становятся частью семейного обряда?</t>
+          <t xml:space="preserve">Невестина причёска меняется в ходе свадьбы. Волосы становятся видимым знаком перехода, который местная традиция оформляет определёнными действиями.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему на свадьбе можно услышать плач?</t>
+          <t xml:space="preserve">Свадебное причитание допускает печаль внутри праздника. Голос выражает переживание перемены, не отменяя радости общего события.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать различие без музыкального образования?</t>
+          <t xml:space="preserve">Причитание и песня по-разному организуют речь. В свадебной записи слышно, как человеческое переживание получает разные музыкальные формы.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вокруг небольшой украшенной вещи строится эпизод?</t>
+          <t xml:space="preserve">Свадебное деревце собирает вокруг себя действия участников. Небольшой предмет становится опорой местного обряда и последовательности встречи.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обычная полоска ткани становится памятной?</t>
+          <t xml:space="preserve">Лента невесты связана с прежним девичеством. Передача или смена украшения превращает личную вещь в знак перемены семейного положения.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто участвует в приготовлении и разделе хлеба?</t>
+          <t xml:space="preserve">Каравай включён в общее свадебное действие. Праздничная еда получает смысл через приготовление, встречу и участие конкретных людей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что поют не для сцены, а для события?</t>
+          <t xml:space="preserve">Каравайная песня сопровождает работу рук. Приготовление свадебного хлеба соединяет общий голос с последовательностью домашнего дела.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник связан с разговорами о будущей семье?</t>
+          <t xml:space="preserve">Покров входит в народные свадебные ожидания осени. Праздничная дата хранит сезонную связь семейных надежд с завершением части хозяйственных работ.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему дорога между домами становится частью праздника?</t>
+          <t xml:space="preserve">Свадебный поезд делает переход видимым для деревни. Движение между домами связывает личное семейное событие с пространством всего поселения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как трапеза выражает отношение к гостю?</t>
+          <t xml:space="preserve">Хлебом и солью встречают входящих в дом. Привычные продукты становятся частью принятия человека и открытого обращения хозяев к гостю.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что надевают после изменения причёски?</t>
+          <t xml:space="preserve">Свадебный убор меняет прежний вид невесты. Слои одежды оформляют переход, который окружающие считывают по местным правилам костюма.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в комнате не все места равноценны?</t>
+          <t xml:space="preserve">В красном углу собираются значимые домашние предметы. Порядок комнаты выделяет место, к которому обращаются в важных семейных обстоятельствах.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может означать место человека на семейном пиру?</t>
+          <t xml:space="preserve">Рассадка делает отношения видимыми за столом. Место гостя связано с местным порядком встречи — близость к другому человеку не случайна.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как песня обращается к конкретному гостю?</t>
+          <t xml:space="preserve">Величальная песня называет достоинства человека. Праздничный голос обращает внимание собрания на того, кому адресованы слова.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему свадебная насмешка понятна участникам обряда?</t>
+          <t xml:space="preserve">Корильная песня включает шутку в свадебное общение. Её смысл зависит от ситуации и границ, которые признают участники конкретной традиции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обмен вещами укрепляет новые связи?</t>
+          <t xml:space="preserve">На свадебный дар отвечают отдариванием. Вещь проходит между людьми и поддерживает связь, которая не исчерпывается одной передачей подарка.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется название одного человека для разных родственников?</t>
+          <t xml:space="preserve">После свадьбы появляются новые названия родства. Свекровь, тёща и зять обозначают разные связи внутри расширившегося семейного круга.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие привычные действия становятся непривычными на новом месте?</t>
+          <t xml:space="preserve">Первое утро в новом доме продолжает свадебную перемену. За торжественным переходом начинается знакомство с повседневным порядком другой семьи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему нельзя собрать русскую свадьбу из случайных обычаев?</t>
+          <t xml:space="preserve">В Большебыкове свадьба имеет свой порядок. Местная запись сохраняет конкретные роли и действия, которые нельзя автоматически приписать всем русским сёлам.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семейный обряд живёт в переселенческой среде?</t>
+          <t xml:space="preserve">Русская свадьба Томского Приобья живёт вдали от прежней родины. Запись позволяет увидеть местное продолжение семейной традиции в новом окружении.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что даёт запись людей, а не только пересказ обряда?</t>
+          <t xml:space="preserve">Северная свадьба Кебы сохраняется в голосах села. Имена исполнителей и обстоятельства записи возвращают обряду конкретное человеческое место.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название традиции охватывает несколько поселений?</t>
+          <t xml:space="preserve">Локня и Ловать задают географию свадебных записей. Речная карта помогает различать местные варианты вместо одной собирательной церемонии.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся, если обряд перестали исполнять целиком?</t>
+          <t xml:space="preserve">Запись из Сланцевского района удерживает семейный обряд во времени. Слышимый голос связывает исследование традиции с конкретным исполнителем.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что изменилось в одежде и способе хранить память?</t>
+          <t xml:space="preserve">Городское свадебное фото выбирает новые позы и декорации. Семейное событие получает другой визуальный язык, сохраняя желание оставить память о встрече.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли рассказать о близких, не зная их точных слов?</t>
+          <t xml:space="preserve">Семейная история складывается из снимков, подписей и свидетельств. Отсутствующий разговор остаётся неизвестным — память сильнее без выдуманной цитаты.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
